--- a/output/REM_2024_P9_SECCION_A_ADOLESCENTES.xlsx
+++ b/output/REM_2024_P9_SECCION_A_ADOLESCENTES.xlsx
@@ -139,7 +139,7 @@
     <t>Centro de Salud Familiar Cristo Vive (ONG)</t>
   </si>
   <si>
-    <t>Centro Comunitario de Salud Familiar Dr. José Symón Ojeda</t>
+    <t>CECOSF Haydeé Sepúlveda</t>
   </si>
   <si>
     <t>Centro Comunitario de Salud Familiar Pucara de Lasana</t>
@@ -190,7 +190,7 @@
     <t>Centro Comunitario de Salud Familiar Sol de Septiembre</t>
   </si>
   <si>
-    <t>Hospital de Til Til</t>
+    <t>Hospital Comunitario de Til Til</t>
   </si>
   <si>
     <t>Centro de Salud Familiar Agustín Cruz Melo</t>
@@ -385,7 +385,7 @@
     <t>Centro Comunitario de Salud Familiar Padre Demetrio Bravo</t>
   </si>
   <si>
-    <t>Centro Comunitario de Salud Familiar Lo Chacón</t>
+    <t>CECOSF Wilma Yoli Gomez Conejera</t>
   </si>
   <si>
     <t>Hospital de Curacaví</t>
@@ -445,7 +445,7 @@
     <t>Centro de Salud Familiar Santa Anselma</t>
   </si>
   <si>
-    <t>Centro de Salud Familiar Maipo</t>
+    <t>Centro de Salud Familiar Dragica Ciudad Pap</t>
   </si>
   <si>
     <t>Centro de Salud Familiar Confraternidad</t>
@@ -1000,7 +1000,7 @@
     <t>Servicio de Salud Metropolitano Central</t>
   </si>
   <si>
-    <t>Servicio de Salud Metropolitano Sur Oriente</t>
+    <t>Servicio de Salud Metropolitano Sur - Oriente</t>
   </si>
   <si>
     <t>Servicio de Salud Metropolitano Oriente</t>
